--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/Mistral-Small-3.2-24B-Instruct-2506/default/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2">
         <v>50</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>426</v>
